--- a/eval/bench_results.xlsx
+++ b/eval/bench_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,130 +464,654 @@
           <t>olympiad_bench</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Qwen3-4B-xcombined-base-grpo_max_tokens40960_temperature0_top_p0.95</t>
+          <t>Qwen3-4B-xcombined-pro-grpo-pass@32_max_tokens40960_temperature0.6_top_p0.95</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>66.7</v>
+        <v>86.7</v>
       </c>
       <c r="C2" t="n">
-        <v>56.7</v>
+        <v>86.7</v>
       </c>
       <c r="D2" t="n">
-        <v>88</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>93</v>
+        <v>99.8</v>
       </c>
       <c r="F2" t="n">
-        <v>39.3</v>
+        <v>56.99999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>62.1</v>
+        <v>82.69999999999999</v>
+      </c>
+      <c r="H2" t="n">
+        <v>85.09999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Qwen3-4B-xcombined-pro-grpo-150step_max_tokens40960_temperature0_top_p0.95</t>
+          <t>Qwen3-4B-pass@32_max_tokens40960_temperature0.6_top_p0.95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>73.3</v>
+        <v>86.7</v>
       </c>
       <c r="C3" t="n">
-        <v>43.3</v>
+        <v>86.7</v>
       </c>
       <c r="D3" t="n">
-        <v>91.60000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>94.39999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>43.4</v>
+        <v>59.2</v>
       </c>
       <c r="G3" t="n">
-        <v>67.60000000000001</v>
+        <v>79.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>84.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Qwen3-4B-xcombined-pro-grpo_max_tokens40960_temperature0_top_p0.95</t>
+          <t>Qwen3-4B-xcombined-pro-wpg-fk1-grpo-v0.001_max_tokens40960_temperature0_top_p0.95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70</v>
+        <v>73.3</v>
       </c>
       <c r="C4" t="n">
-        <v>70</v>
+        <v>76.7</v>
       </c>
       <c r="D4" t="n">
-        <v>92.80000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>95</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="F4" t="n">
         <v>42.6</v>
       </c>
       <c r="G4" t="n">
-        <v>64.60000000000001</v>
+        <v>65.60000000000001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Qwen3-4B-xcombined-pro-wtrapo-grpo_max_tokens40960_temperature0_top_p0.95</t>
+          <t>Qwen3-4B-xcombined-pro-wpg-fk3-grpo_max_tokens40960_temperature0.6_top_p0.95</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73.3</v>
+        <v>70</v>
       </c>
       <c r="C5" t="n">
-        <v>63.3</v>
+        <v>70</v>
       </c>
       <c r="D5" t="n">
-        <v>84.3</v>
+        <v>91.60000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F5" t="n">
-        <v>44.5</v>
+        <v>44.9</v>
       </c>
       <c r="G5" t="n">
-        <v>64</v>
+        <v>68.89999999999999</v>
+      </c>
+      <c r="H5" t="n">
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Qwen3-4B_max_tokens40960_temperature0_top_p0.95</t>
+          <t>Qwen3-4B-xcombined-pro-wpg-fk1-ISdt-grpo-v0.001_max_tokens40960_temperature0_top_p0.95</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C6" t="n">
         <v>63.3</v>
       </c>
       <c r="D6" t="n">
-        <v>86.7</v>
+        <v>91.60000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>94</v>
+        <v>95.39999999999999</v>
       </c>
       <c r="F6" t="n">
         <v>44.5</v>
       </c>
       <c r="G6" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>73.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-xcombined-pro-wpg-fk3-grpo-v0.01_max_tokens40960_temperature0.6_top_p0.95</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="C7" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>88</v>
+      </c>
+      <c r="E7" t="n">
+        <v>97</v>
+      </c>
+      <c r="F7" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>68.30000000000001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-xcombined-pro-grpo_max_tokens40960_temperature0_top_p0.95</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>70</v>
+      </c>
+      <c r="C8" t="n">
+        <v>70</v>
+      </c>
+      <c r="D8" t="n">
+        <v>92.80000000000001</v>
+      </c>
+      <c r="E8" t="n">
+        <v>95</v>
+      </c>
+      <c r="F8" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>64.60000000000001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>72.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-xcombined-pro-wpg-fk3dt-grpo-v0.01_max_tokens40960_temperature0_top_p0.95</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="C9" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="D9" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="E9" t="n">
+        <v>94.19999999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>67</v>
+      </c>
+      <c r="H9" t="n">
+        <v>71.59999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-xcombined-pro-wpg-fk3-grpo_max_tokens40960_temperature0.0_top_p0.95</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="C10" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="F10" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>65</v>
+      </c>
+      <c r="H10" t="n">
+        <v>71.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-xcombined-pro-wpg-fk3-grpo-v0.01-debug_max_tokens40960_temperature0_top_p0.95</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>80</v>
+      </c>
+      <c r="C11" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="E11" t="n">
+        <v>96.39999999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="G11" t="n">
+        <v>68.89999999999999</v>
+      </c>
+      <c r="H11" t="n">
+        <v>70.89999999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-xcombined-pro-wtrapo-grpo_max_tokens40960_temperature0_top_p0.95</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>95</v>
+      </c>
+      <c r="F12" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>64</v>
+      </c>
+      <c r="H12" t="n">
+        <v>70.7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-xcombined-pro-wpg-fk3-grpo-v0.01_max_tokens40960_temperature0.0_top_p0.95</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>80</v>
+      </c>
+      <c r="C13" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>96</v>
+      </c>
+      <c r="F13" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>68.10000000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Qwen3-4B_max_tokens40960_temperature0_top_p0.95</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>70</v>
+      </c>
+      <c r="C14" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="E14" t="n">
+        <v>94</v>
+      </c>
+      <c r="F14" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="G14" t="n">
         <v>64.09999999999999</v>
+      </c>
+      <c r="H14" t="n">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-xcombined-pro-wpggspo-fk3-grpo-v0.01_max_tokens40960_temperature0_top_p0.95</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="C15" t="n">
+        <v>60</v>
+      </c>
+      <c r="D15" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="E15" t="n">
+        <v>93.60000000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>69.89999999999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-xcombined-pro-wdft-grpo-v0.001_max_tokens40960_temperature0_top_p0.95</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="C16" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="F16" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="H16" t="n">
+        <v>69.8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-xcombined-pro-grpo-150step_max_tokens40960_temperature0_top_p0.95</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="C17" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>91.60000000000001</v>
+      </c>
+      <c r="E17" t="n">
+        <v>94.39999999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="G17" t="n">
+        <v>67.60000000000001</v>
+      </c>
+      <c r="H17" t="n">
+        <v>68.89999999999999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-xcombined-pro-wpg-fk1-advdt-grpo-v0.001_max_tokens40960_temperature0_top_p0.95</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="C18" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>96.39999999999999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>43</v>
+      </c>
+      <c r="G18" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>68.40000000000001</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-xcombined-base-grpo_max_tokens40960_temperature0_top_p0.95</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="C19" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="D19" t="n">
+        <v>88</v>
+      </c>
+      <c r="E19" t="n">
+        <v>93</v>
+      </c>
+      <c r="F19" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="G19" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>67.60000000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-xcombined-pro-wpg-fk3-advshift-grpo-v0.001_max_tokens40960_temperature0_top_p0.95</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>60</v>
+      </c>
+      <c r="C20" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="E20" t="n">
+        <v>88</v>
+      </c>
+      <c r="F20" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="G20" t="n">
+        <v>56.39999999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>60.4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-xcombined-pro-wfkl-k3-grpo-v0.001_max_tokens40960_temperature0_top_p0.95</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="D21" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>90</v>
+      </c>
+      <c r="F21" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="G21" t="n">
+        <v>57.49999999999999</v>
+      </c>
+      <c r="H21" t="n">
+        <v>59.4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-xcombined-pro-wrkl-k3-grpo-v0.001_max_tokens40960_temperature0_top_p0.95</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="C22" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-xcombined-pro-wfkl-k1-grpo-v0.001_max_tokens40960_temperature0_top_p0.95</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="C23" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="D23" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="E23" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="F23" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="G23" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>54.8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-xcombined-pro-wsft-grpo_max_tokens40960_temperature0_top_p0.95</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>40</v>
+      </c>
+      <c r="C24" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="D24" t="n">
+        <v>65.10000000000001</v>
+      </c>
+      <c r="E24" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="F24" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>47</v>
+      </c>
+      <c r="H24" t="n">
+        <v>48.8</v>
       </c>
     </row>
   </sheetData>
